--- a/data/test-data-result.xlsx
+++ b/data/test-data-result.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="6">
   <si>
     <t>TC01</t>
   </si>
@@ -426,7 +426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A47E47CB-3588-43E4-95CC-22B2A2B988CB}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1">
@@ -528,6 +528,17 @@
         <v>2</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/test-data-result.xlsx
+++ b/data/test-data-result.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="6">
   <si>
     <t>TC01</t>
   </si>
@@ -426,7 +426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A47E47CB-3588-43E4-95CC-22B2A2B988CB}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1">
@@ -539,6 +539,17 @@
         <v>2</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
